--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/44.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/44.xlsx
@@ -426,13 +426,13 @@
         <v>-13.8641157620535</v>
       </c>
       <c r="E2">
-        <v>-8.011327206934263</v>
+        <v>-4.686536179012646</v>
       </c>
       <c r="F2">
-        <v>2.732034242088528</v>
+        <v>5.329645311135273</v>
       </c>
       <c r="G2">
-        <v>-16.49107834420433</v>
+        <v>-17.72755961686297</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.31722564581441</v>
       </c>
       <c r="E3">
-        <v>-8.784464107896396</v>
+        <v>-5.509710970016313</v>
       </c>
       <c r="F3">
-        <v>2.166564145180696</v>
+        <v>5.28394593825763</v>
       </c>
       <c r="G3">
-        <v>-15.7826358295659</v>
+        <v>-17.69074289663909</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.53941139934548</v>
       </c>
       <c r="E4">
-        <v>-10.17533304846823</v>
+        <v>-6.68347078858273</v>
       </c>
       <c r="F4">
-        <v>2.990196599905799</v>
+        <v>5.30525651806205</v>
       </c>
       <c r="G4">
-        <v>-15.85768951507122</v>
+        <v>-16.61956875000056</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.62166906558467</v>
       </c>
       <c r="E5">
-        <v>-10.32597002321976</v>
+        <v>-6.8985822159409</v>
       </c>
       <c r="F5">
-        <v>3.184674071795845</v>
+        <v>5.614769371178864</v>
       </c>
       <c r="G5">
-        <v>-15.70260214875302</v>
+        <v>-15.95300518934818</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.58917299280653</v>
       </c>
       <c r="E6">
-        <v>-12.31758021587141</v>
+        <v>-7.992330418334497</v>
       </c>
       <c r="F6">
-        <v>3.080465452523667</v>
+        <v>5.4151676185351</v>
       </c>
       <c r="G6">
-        <v>-15.11681241500509</v>
+        <v>-15.81219990131566</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.507120875161071</v>
       </c>
       <c r="E7">
-        <v>-13.12081128609325</v>
+        <v>-8.363170657528437</v>
       </c>
       <c r="F7">
-        <v>2.092817908779067</v>
+        <v>5.79945885383743</v>
       </c>
       <c r="G7">
-        <v>-15.05445086432947</v>
+        <v>-14.56032045705864</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.411289849359918</v>
       </c>
       <c r="E8">
-        <v>-12.06740322529771</v>
+        <v>-9.679913082374728</v>
       </c>
       <c r="F8">
-        <v>3.003220192212613</v>
+        <v>5.645276485889164</v>
       </c>
       <c r="G8">
-        <v>-12.93570631290066</v>
+        <v>-14.12752296709454</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.335719863301057</v>
       </c>
       <c r="E9">
-        <v>-12.65124090728549</v>
+        <v>-10.03079298794154</v>
       </c>
       <c r="F9">
-        <v>2.941725509698389</v>
+        <v>5.581750646503275</v>
       </c>
       <c r="G9">
-        <v>-13.35987529199113</v>
+        <v>-12.883078923433</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.297614698048204</v>
       </c>
       <c r="E10">
-        <v>-14.50659254279217</v>
+        <v>-11.36175600836405</v>
       </c>
       <c r="F10">
-        <v>3.100594780411695</v>
+        <v>5.86701221553573</v>
       </c>
       <c r="G10">
-        <v>-12.77541964872926</v>
+        <v>-12.46599550516281</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.296461579478065</v>
       </c>
       <c r="E11">
-        <v>-14.14160833156623</v>
+        <v>-11.61315819627857</v>
       </c>
       <c r="F11">
-        <v>3.368611396852669</v>
+        <v>5.755888385184981</v>
       </c>
       <c r="G11">
-        <v>-11.99187123369368</v>
+        <v>-12.04629481544003</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.33430241836433</v>
       </c>
       <c r="E12">
-        <v>-15.68978015106595</v>
+        <v>-11.81865493941976</v>
       </c>
       <c r="F12">
-        <v>3.611511913640763</v>
+        <v>5.838630691581013</v>
       </c>
       <c r="G12">
-        <v>-10.80556847207624</v>
+        <v>-11.21078344543523</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.393540945954692</v>
       </c>
       <c r="E13">
-        <v>-15.01044352787506</v>
+        <v>-12.54562059008377</v>
       </c>
       <c r="F13">
-        <v>3.129685386863208</v>
+        <v>6.363742728624453</v>
       </c>
       <c r="G13">
-        <v>-11.31899228187539</v>
+        <v>-10.57917775485785</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.476264800274796</v>
       </c>
       <c r="E14">
-        <v>-16.11269335385059</v>
+        <v>-14.18049069598928</v>
       </c>
       <c r="F14">
-        <v>4.707692154500154</v>
+        <v>6.32239891155073</v>
       </c>
       <c r="G14">
-        <v>-9.711110399801864</v>
+        <v>-9.509102731692177</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.571647495716745</v>
       </c>
       <c r="E15">
-        <v>-18.19780063984678</v>
+        <v>-14.73014329556239</v>
       </c>
       <c r="F15">
-        <v>3.830005413272771</v>
+        <v>6.537110085621556</v>
       </c>
       <c r="G15">
-        <v>-9.428211421281125</v>
+        <v>-9.222478220639919</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6842766960794778</v>
       </c>
       <c r="E16">
-        <v>-19.10027684788673</v>
+        <v>-15.04424651484785</v>
       </c>
       <c r="F16">
-        <v>4.494790134837042</v>
+        <v>6.981076908621562</v>
       </c>
       <c r="G16">
-        <v>-8.539259414868528</v>
+        <v>-8.382527279457928</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1848876107123716</v>
       </c>
       <c r="E17">
-        <v>-19.75943301725026</v>
+        <v>-16.96935133455502</v>
       </c>
       <c r="F17">
-        <v>4.379077149074785</v>
+        <v>7.084793477656477</v>
       </c>
       <c r="G17">
-        <v>-8.750608327125217</v>
+        <v>-7.482538350286402</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.028761312837156</v>
       </c>
       <c r="E18">
-        <v>-20.04353759113648</v>
+        <v>-17.1709648251075</v>
       </c>
       <c r="F18">
-        <v>4.445522155188138</v>
+        <v>7.207926978613012</v>
       </c>
       <c r="G18">
-        <v>-7.590359491154789</v>
+        <v>-6.844472372218315</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.835817628561729</v>
       </c>
       <c r="E19">
-        <v>-20.28793331154602</v>
+        <v>-18.39524015301781</v>
       </c>
       <c r="F19">
-        <v>4.294262267436949</v>
+        <v>7.118862572198815</v>
       </c>
       <c r="G19">
-        <v>-7.231891205071979</v>
+        <v>-6.432298459151713</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.595628672081356</v>
       </c>
       <c r="E20">
-        <v>-20.88333353386211</v>
+        <v>-19.0130386440087</v>
       </c>
       <c r="F20">
-        <v>4.895423402261801</v>
+        <v>7.369379098888247</v>
       </c>
       <c r="G20">
-        <v>-6.715958469720762</v>
+        <v>-5.836513489736705</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.288041898164674</v>
       </c>
       <c r="E21">
-        <v>-23.42119069280052</v>
+        <v>-19.10014809833566</v>
       </c>
       <c r="F21">
-        <v>5.032022843718245</v>
+        <v>7.466679134021077</v>
       </c>
       <c r="G21">
-        <v>-7.004179451090487</v>
+        <v>-5.540423724169366</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.899404763504916</v>
       </c>
       <c r="E22">
-        <v>-21.90386892702163</v>
+        <v>-19.96095513715359</v>
       </c>
       <c r="F22">
-        <v>5.176592836324425</v>
+        <v>7.389828176593756</v>
       </c>
       <c r="G22">
-        <v>-5.30451945366096</v>
+        <v>-5.261282912487533</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.410264690249466</v>
       </c>
       <c r="E23">
-        <v>-22.53848377066676</v>
+        <v>-19.70625114623583</v>
       </c>
       <c r="F23">
-        <v>5.400802071035751</v>
+        <v>7.372198861527377</v>
       </c>
       <c r="G23">
-        <v>-6.612554708700539</v>
+        <v>-4.657023466129772</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.811747679548653</v>
       </c>
       <c r="E24">
-        <v>-23.08618020770587</v>
+        <v>-20.27012018817383</v>
       </c>
       <c r="F24">
-        <v>5.125959707195708</v>
+        <v>7.3421721999107</v>
       </c>
       <c r="G24">
-        <v>-5.330465033407444</v>
+        <v>-4.427277942111803</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.095323216590778</v>
       </c>
       <c r="E25">
-        <v>-24.60633031039697</v>
+        <v>-21.3220953910623</v>
       </c>
       <c r="F25">
-        <v>4.211695574930311</v>
+        <v>7.140809338168586</v>
       </c>
       <c r="G25">
-        <v>-6.420038402551845</v>
+        <v>-4.335946264080887</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.264595375071837</v>
       </c>
       <c r="E26">
-        <v>-24.10374605476814</v>
+        <v>-20.14459768230354</v>
       </c>
       <c r="F26">
-        <v>4.952980026143115</v>
+        <v>7.227589107285861</v>
       </c>
       <c r="G26">
-        <v>-5.405205429561835</v>
+        <v>-4.350501165176343</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.32701639238999</v>
       </c>
       <c r="E27">
-        <v>-23.48106754047057</v>
+        <v>-20.83181710058894</v>
       </c>
       <c r="F27">
-        <v>4.821339191959829</v>
+        <v>7.444903011736284</v>
       </c>
       <c r="G27">
-        <v>-5.593218201290859</v>
+        <v>-4.051343774714446</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.299026726370021</v>
       </c>
       <c r="E28">
-        <v>-23.75570279253618</v>
+        <v>-20.49755004032144</v>
       </c>
       <c r="F28">
-        <v>5.433776063871588</v>
+        <v>7.273855083467019</v>
       </c>
       <c r="G28">
-        <v>-6.658438544889354</v>
+        <v>-4.651603560358621</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.200001927394519</v>
       </c>
       <c r="E29">
-        <v>-23.02725029221788</v>
+        <v>-20.38764776224383</v>
       </c>
       <c r="F29">
-        <v>4.416045529526921</v>
+        <v>6.820554216572268</v>
       </c>
       <c r="G29">
-        <v>-5.771229210491327</v>
+        <v>-4.621371137993529</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.052403034677991</v>
       </c>
       <c r="E30">
-        <v>-21.86533543234987</v>
+        <v>-20.11753951052228</v>
       </c>
       <c r="F30">
-        <v>4.85768464012506</v>
+        <v>7.056973586800859</v>
       </c>
       <c r="G30">
-        <v>-5.698266731403484</v>
+        <v>-4.397763474509267</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.879649921591104</v>
       </c>
       <c r="E31">
-        <v>-23.88715608417833</v>
+        <v>-20.45452277099622</v>
       </c>
       <c r="F31">
-        <v>4.333294939456862</v>
+        <v>7.10819982698998</v>
       </c>
       <c r="G31">
-        <v>-6.324767110932939</v>
+        <v>-5.013724278124398</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.698791441260349</v>
       </c>
       <c r="E32">
-        <v>-21.86911070144414</v>
+        <v>-20.17281875325575</v>
       </c>
       <c r="F32">
-        <v>5.067463714679619</v>
+        <v>7.062154196537967</v>
       </c>
       <c r="G32">
-        <v>-5.861934309820375</v>
+        <v>-4.788490120759873</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.527013989384973</v>
       </c>
       <c r="E33">
-        <v>-23.25623344540098</v>
+        <v>-19.79760102932543</v>
       </c>
       <c r="F33">
-        <v>4.836425419099614</v>
+        <v>7.318576982809359</v>
       </c>
       <c r="G33">
-        <v>-6.253154386798702</v>
+        <v>-5.184336437153651</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.36792452652672</v>
       </c>
       <c r="E34">
-        <v>-22.48789350351902</v>
+        <v>-19.95325923656868</v>
       </c>
       <c r="F34">
-        <v>4.758388239551484</v>
+        <v>7.232131874122814</v>
       </c>
       <c r="G34">
-        <v>-6.549586159907477</v>
+        <v>-4.970427689825375</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.225270889074369</v>
       </c>
       <c r="E35">
-        <v>-22.1856393961433</v>
+        <v>-18.88539800036274</v>
       </c>
       <c r="F35">
-        <v>4.994822520393324</v>
+        <v>7.531437584102331</v>
       </c>
       <c r="G35">
-        <v>-6.373180758630544</v>
+        <v>-5.516658116156462</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.089167297197152</v>
       </c>
       <c r="E36">
-        <v>-20.70717507551951</v>
+        <v>-17.97671274139218</v>
       </c>
       <c r="F36">
-        <v>4.869584966233679</v>
+        <v>7.561865175541962</v>
       </c>
       <c r="G36">
-        <v>-6.713081429181356</v>
+        <v>-5.581871905297881</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.953080033042296</v>
       </c>
       <c r="E37">
-        <v>-21.40967415826896</v>
+        <v>-18.07897726384344</v>
       </c>
       <c r="F37">
-        <v>5.091625535084475</v>
+        <v>7.817406578896777</v>
       </c>
       <c r="G37">
-        <v>-7.262003533185879</v>
+        <v>-5.668807089437362</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.802459224579894</v>
       </c>
       <c r="E38">
-        <v>-20.0420341286369</v>
+        <v>-18.22996310834625</v>
       </c>
       <c r="F38">
-        <v>5.188178382819979</v>
+        <v>7.742472463639533</v>
       </c>
       <c r="G38">
-        <v>-6.669985868215849</v>
+        <v>-6.01958151121016</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.626162087914145</v>
       </c>
       <c r="E39">
-        <v>-18.59169535510485</v>
+        <v>-16.84657410137044</v>
       </c>
       <c r="F39">
-        <v>4.49439914542292</v>
+        <v>8.195229921518049</v>
       </c>
       <c r="G39">
-        <v>-7.094083051830064</v>
+        <v>-5.934288485418489</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.415816990305955</v>
       </c>
       <c r="E40">
-        <v>-20.25034674905632</v>
+        <v>-16.73390163133917</v>
       </c>
       <c r="F40">
-        <v>5.499893036493433</v>
+        <v>8.061297823098618</v>
       </c>
       <c r="G40">
-        <v>-7.703603148538918</v>
+        <v>-6.579672380575467</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.165989221050358</v>
       </c>
       <c r="E41">
-        <v>-19.08724407074941</v>
+        <v>-15.88755192114296</v>
       </c>
       <c r="F41">
-        <v>5.330765263863858</v>
+        <v>7.928189121877572</v>
       </c>
       <c r="G41">
-        <v>-7.795441311020511</v>
+        <v>-6.418923614611439</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.878481510937965</v>
       </c>
       <c r="E42">
-        <v>-18.34064619015293</v>
+        <v>-15.07272093169087</v>
       </c>
       <c r="F42">
-        <v>5.20083417999995</v>
+        <v>8.23126224680502</v>
       </c>
       <c r="G42">
-        <v>-7.658267568714236</v>
+        <v>-7.172953645927596</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.55364729776525</v>
       </c>
       <c r="E43">
-        <v>-18.27026587104239</v>
+        <v>-14.98582744435281</v>
       </c>
       <c r="F43">
-        <v>5.108103419460963</v>
+        <v>8.300286789010693</v>
       </c>
       <c r="G43">
-        <v>-7.223301855367216</v>
+        <v>-6.756221372804911</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.199294952666903</v>
       </c>
       <c r="E44">
-        <v>-16.86082376942593</v>
+        <v>-14.03321782241086</v>
       </c>
       <c r="F44">
-        <v>5.661121497569912</v>
+        <v>8.420429883643122</v>
       </c>
       <c r="G44">
-        <v>-8.20639078487388</v>
+        <v>-7.298016144075697</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.819013325112045</v>
       </c>
       <c r="E45">
-        <v>-17.74010013900538</v>
+        <v>-13.04294688017537</v>
       </c>
       <c r="F45">
-        <v>5.701535886417695</v>
+        <v>8.56523016238728</v>
       </c>
       <c r="G45">
-        <v>-7.630360014407531</v>
+        <v>-7.937940972292656</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.422509317889857</v>
       </c>
       <c r="E46">
-        <v>-15.84311255996729</v>
+        <v>-13.23014042100804</v>
       </c>
       <c r="F46">
-        <v>5.008336506202595</v>
+        <v>8.106980628628206</v>
       </c>
       <c r="G46">
-        <v>-8.168019366245993</v>
+        <v>-7.988500652044156</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.015808784239542</v>
       </c>
       <c r="E47">
-        <v>-14.75363385881562</v>
+        <v>-12.34379528575373</v>
       </c>
       <c r="F47">
-        <v>5.63958228836232</v>
+        <v>8.187043994843583</v>
       </c>
       <c r="G47">
-        <v>-8.995019708883765</v>
+        <v>-8.152458023110661</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.6070748461162544</v>
       </c>
       <c r="E48">
-        <v>-15.8490184264712</v>
+        <v>-11.96902195543518</v>
       </c>
       <c r="F48">
-        <v>5.391801030836931</v>
+        <v>8.355267190269302</v>
       </c>
       <c r="G48">
-        <v>-8.390000535849991</v>
+        <v>-8.054555100943913</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.2015463112035765</v>
       </c>
       <c r="E49">
-        <v>-14.82899387830463</v>
+        <v>-11.645179455593</v>
       </c>
       <c r="F49">
-        <v>5.847389848498215</v>
+        <v>8.318661634739591</v>
       </c>
       <c r="G49">
-        <v>-8.501258721972579</v>
+        <v>-8.238090445699177</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.1959754749583016</v>
       </c>
       <c r="E50">
-        <v>-13.79077826453532</v>
+        <v>-11.25035857420949</v>
       </c>
       <c r="F50">
-        <v>5.283593053744037</v>
+        <v>8.279867532531684</v>
       </c>
       <c r="G50">
-        <v>-7.617802332924276</v>
+        <v>-8.357351869365823</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5798857433029686</v>
       </c>
       <c r="E51">
-        <v>-13.08829579463117</v>
+        <v>-10.4811256918927</v>
       </c>
       <c r="F51">
-        <v>4.94715494656663</v>
+        <v>7.959196570499162</v>
       </c>
       <c r="G51">
-        <v>-9.137732145840086</v>
+        <v>-9.259435921071718</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9484670982939336</v>
       </c>
       <c r="E52">
-        <v>-13.49276873913357</v>
+        <v>-9.224941241373736</v>
       </c>
       <c r="F52">
-        <v>5.269086683786213</v>
+        <v>8.387271993243862</v>
       </c>
       <c r="G52">
-        <v>-9.64405342497912</v>
+        <v>-9.112995340839289</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.296697857418188</v>
       </c>
       <c r="E53">
-        <v>-14.00266264669409</v>
+        <v>-8.90811351545919</v>
       </c>
       <c r="F53">
-        <v>6.135641823854775</v>
+        <v>8.286103482339959</v>
       </c>
       <c r="G53">
-        <v>-9.3161412935907</v>
+        <v>-9.358551534101039</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.624666412988748</v>
       </c>
       <c r="E54">
-        <v>-11.11059885991769</v>
+        <v>-8.247437270750765</v>
       </c>
       <c r="F54">
-        <v>5.046878784720051</v>
+        <v>8.111268258305095</v>
       </c>
       <c r="G54">
-        <v>-9.748594165268774</v>
+        <v>-9.613362816938286</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.928366312935183</v>
       </c>
       <c r="E55">
-        <v>-12.64637749682411</v>
+        <v>-8.138029224820807</v>
       </c>
       <c r="F55">
-        <v>5.386834139889745</v>
+        <v>7.923861730565346</v>
       </c>
       <c r="G55">
-        <v>-9.739027091714638</v>
+        <v>-9.852914297640478</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.209003216584471</v>
       </c>
       <c r="E56">
-        <v>-12.35745519780109</v>
+        <v>-7.435226957644645</v>
       </c>
       <c r="F56">
-        <v>4.56605623923469</v>
+        <v>8.292879527694859</v>
       </c>
       <c r="G56">
-        <v>-9.021993921999147</v>
+        <v>-10.14876126396084</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.463754501975629</v>
       </c>
       <c r="E57">
-        <v>-11.8697643579831</v>
+        <v>-7.127195733316087</v>
       </c>
       <c r="F57">
-        <v>4.763172889670054</v>
+        <v>8.22228440089348</v>
       </c>
       <c r="G57">
-        <v>-10.06988544837413</v>
+        <v>-10.04137220132229</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.693062308344723</v>
       </c>
       <c r="E58">
-        <v>-10.52718480548505</v>
+        <v>-6.777732072811039</v>
       </c>
       <c r="F58">
-        <v>5.201723846590557</v>
+        <v>8.086085889259991</v>
       </c>
       <c r="G58">
-        <v>-11.01141262936257</v>
+        <v>-10.47044676949946</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.895693205031774</v>
       </c>
       <c r="E59">
-        <v>-11.95345571938972</v>
+        <v>-7.147787355064588</v>
       </c>
       <c r="F59">
-        <v>5.427858207145988</v>
+        <v>8.168296383783424</v>
       </c>
       <c r="G59">
-        <v>-11.41886631620843</v>
+        <v>-10.25202665551774</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.071775329603791</v>
       </c>
       <c r="E60">
-        <v>-12.63319935729043</v>
+        <v>-7.035173029991862</v>
       </c>
       <c r="F60">
-        <v>4.915685268934276</v>
+        <v>7.879520880228295</v>
       </c>
       <c r="G60">
-        <v>-10.12493299807775</v>
+        <v>-10.89394739797461</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.222734179621346</v>
       </c>
       <c r="E61">
-        <v>-10.69857122401542</v>
+        <v>-5.767887045601629</v>
       </c>
       <c r="F61">
-        <v>5.005750343171056</v>
+        <v>8.006564275326044</v>
       </c>
       <c r="G61">
-        <v>-10.69324510216047</v>
+        <v>-10.77698995640962</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.348324911764543</v>
       </c>
       <c r="E62">
-        <v>-10.48485942887372</v>
+        <v>-6.300885267762175</v>
       </c>
       <c r="F62">
-        <v>5.214389584179361</v>
+        <v>7.68046916353999</v>
       </c>
       <c r="G62">
-        <v>-10.18870304546029</v>
+        <v>-10.95670317108349</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.452194533817021</v>
       </c>
       <c r="E63">
-        <v>-11.05245390137009</v>
+        <v>-5.538268451085834</v>
       </c>
       <c r="F63">
-        <v>4.406971592996655</v>
+        <v>8.075438054664406</v>
       </c>
       <c r="G63">
-        <v>-11.10371158826449</v>
+        <v>-11.14766608420047</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.53314818161182</v>
       </c>
       <c r="E64">
-        <v>-9.619126681424538</v>
+        <v>-5.845697459772292</v>
       </c>
       <c r="F64">
-        <v>4.548889153179072</v>
+        <v>7.835826156465426</v>
       </c>
       <c r="G64">
-        <v>-11.16929088164866</v>
+        <v>-10.76211393372945</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.595457162818589</v>
       </c>
       <c r="E65">
-        <v>-6.924411037170009</v>
+        <v>-5.270677045427131</v>
       </c>
       <c r="F65">
-        <v>4.67277481173735</v>
+        <v>7.757174328304419</v>
       </c>
       <c r="G65">
-        <v>-11.56683679277126</v>
+        <v>-11.64477274030517</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.637986333756838</v>
       </c>
       <c r="E66">
-        <v>-9.69342763202572</v>
+        <v>-5.560421680292469</v>
       </c>
       <c r="F66">
-        <v>4.844750511497749</v>
+        <v>8.036950448395535</v>
       </c>
       <c r="G66">
-        <v>-11.6734961522966</v>
+        <v>-11.10496213492363</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.664799019534445</v>
       </c>
       <c r="E67">
-        <v>-9.846751734504416</v>
+        <v>-5.958627428905705</v>
       </c>
       <c r="F67">
-        <v>4.933289732978571</v>
+        <v>7.500431792215545</v>
       </c>
       <c r="G67">
-        <v>-11.43121122200751</v>
+        <v>-11.17116278552049</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.676500768883097</v>
       </c>
       <c r="E68">
-        <v>-9.515387768952969</v>
+        <v>-5.647510368562799</v>
       </c>
       <c r="F68">
-        <v>4.835736217420485</v>
+        <v>7.8235977968653</v>
       </c>
       <c r="G68">
-        <v>-11.25416357756117</v>
+        <v>-12.21590967003548</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.67644704647787</v>
       </c>
       <c r="E69">
-        <v>-9.411653009692728</v>
+        <v>-6.111851854312604</v>
       </c>
       <c r="F69">
-        <v>5.116836068621275</v>
+        <v>7.93709241472286</v>
       </c>
       <c r="G69">
-        <v>-11.61593967704091</v>
+        <v>-11.65130873938902</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.669153518628977</v>
       </c>
       <c r="E70">
-        <v>-7.509843552306515</v>
+        <v>-5.662515921079404</v>
       </c>
       <c r="F70">
-        <v>4.40435726547342</v>
+        <v>7.66986109057974</v>
       </c>
       <c r="G70">
-        <v>-11.45687484133816</v>
+        <v>-11.94596390080355</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.656114752402957</v>
       </c>
       <c r="E71">
-        <v>-7.744857168333263</v>
+        <v>-5.429005767552244</v>
       </c>
       <c r="F71">
-        <v>5.059819540286584</v>
+        <v>7.716892478241085</v>
       </c>
       <c r="G71">
-        <v>-11.5714082065503</v>
+        <v>-11.78124680306103</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.645947822006037</v>
       </c>
       <c r="E72">
-        <v>-9.496029650967944</v>
+        <v>-5.468461275138115</v>
       </c>
       <c r="F72">
-        <v>4.921659454643266</v>
+        <v>7.969642283448464</v>
       </c>
       <c r="G72">
-        <v>-12.720382542004</v>
+        <v>-11.50655470016245</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.640284238668268</v>
       </c>
       <c r="E73">
-        <v>-9.60985671374752</v>
+        <v>-5.55410049265608</v>
       </c>
       <c r="F73">
-        <v>4.133287286785727</v>
+        <v>7.848594611612178</v>
       </c>
       <c r="G73">
-        <v>-11.23284554260243</v>
+        <v>-11.79365045061341</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.648035211808495</v>
       </c>
       <c r="E74">
-        <v>-9.343918286196098</v>
+        <v>-6.386192228374154</v>
       </c>
       <c r="F74">
-        <v>4.296416022684228</v>
+        <v>7.792840515199354</v>
       </c>
       <c r="G74">
-        <v>-11.94053877354321</v>
+        <v>-11.76560061072648</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.67037224245099</v>
       </c>
       <c r="E75">
-        <v>-10.97508788081118</v>
+        <v>-6.195626279945721</v>
       </c>
       <c r="F75">
-        <v>5.097830006931443</v>
+        <v>8.061077477369473</v>
       </c>
       <c r="G75">
-        <v>-10.83091749668365</v>
+        <v>-11.39999454893157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.712644547891487</v>
       </c>
       <c r="E76">
-        <v>-11.20858557470437</v>
+        <v>-6.44706169355084</v>
       </c>
       <c r="F76">
-        <v>4.735079637571512</v>
+        <v>7.642029602580482</v>
       </c>
       <c r="G76">
-        <v>-11.98356906589394</v>
+        <v>-11.28640105177223</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.775383214271629</v>
       </c>
       <c r="E77">
-        <v>-10.94515153358182</v>
+        <v>-7.844725287850091</v>
       </c>
       <c r="F77">
-        <v>4.928117406915492</v>
+        <v>7.942120604857854</v>
       </c>
       <c r="G77">
-        <v>-11.07207066919249</v>
+        <v>-11.58219058171159</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.855163215283038</v>
       </c>
       <c r="E78">
-        <v>-10.32212414953296</v>
+        <v>-7.514540834314897</v>
       </c>
       <c r="F78">
-        <v>4.713296888347496</v>
+        <v>8.122257380270634</v>
       </c>
       <c r="G78">
-        <v>-11.14035599934535</v>
+        <v>-11.65751839539899</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.948917381797615</v>
       </c>
       <c r="E79">
-        <v>-12.06119002115577</v>
+        <v>-8.88643790555491</v>
       </c>
       <c r="F79">
-        <v>4.386105018120135</v>
+        <v>7.987192075244175</v>
       </c>
       <c r="G79">
-        <v>-9.587468146711331</v>
+        <v>-10.87034104538176</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.04482813513217</v>
       </c>
       <c r="E80">
-        <v>-11.40195494077706</v>
+        <v>-8.011019869296225</v>
       </c>
       <c r="F80">
-        <v>4.870994847553243</v>
+        <v>8.204961581766137</v>
       </c>
       <c r="G80">
-        <v>-10.65062208596596</v>
+        <v>-11.26269026939574</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.135398403493877</v>
       </c>
       <c r="E81">
-        <v>-13.26399739972804</v>
+        <v>-9.376545914363952</v>
       </c>
       <c r="F81">
-        <v>4.872482595408671</v>
+        <v>8.293393115484594</v>
       </c>
       <c r="G81">
-        <v>-10.13518539208706</v>
+        <v>-10.75550483379705</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.205189583422453</v>
       </c>
       <c r="E82">
-        <v>-13.57966222647163</v>
+        <v>-9.961131174390193</v>
       </c>
       <c r="F82">
-        <v>4.651335006618092</v>
+        <v>7.843914335786361</v>
       </c>
       <c r="G82">
-        <v>-10.41944065242288</v>
+        <v>-10.7377152201532</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.244795129360657</v>
       </c>
       <c r="E83">
-        <v>-13.07027501069274</v>
+        <v>-11.0971175359573</v>
       </c>
       <c r="F83">
-        <v>5.15302578371478</v>
+        <v>8.358738049687032</v>
       </c>
       <c r="G83">
-        <v>-10.3988705957895</v>
+        <v>-10.67029926794918</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.240649249237848</v>
       </c>
       <c r="E84">
-        <v>-14.76291213291528</v>
+        <v>-11.99686508415683</v>
       </c>
       <c r="F84">
-        <v>4.343018316030922</v>
+        <v>8.320134471981769</v>
       </c>
       <c r="G84">
-        <v>-9.52899399473187</v>
+        <v>-10.20486355447928</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.183939148822783</v>
       </c>
       <c r="E85">
-        <v>-16.89801577683977</v>
+        <v>-12.72986950408714</v>
       </c>
       <c r="F85">
-        <v>5.394970364520042</v>
+        <v>8.541113073822176</v>
       </c>
       <c r="G85">
-        <v>-9.670233971738803</v>
+        <v>-10.20400070339191</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.067227011651838</v>
       </c>
       <c r="E86">
-        <v>-17.76684681993727</v>
+        <v>-13.10954777698032</v>
       </c>
       <c r="F86">
-        <v>4.770938005703896</v>
+        <v>8.565258326878975</v>
       </c>
       <c r="G86">
-        <v>-8.624055093815592</v>
+        <v>-9.883574882118513</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.885700274018518</v>
       </c>
       <c r="E87">
-        <v>-17.57709074771718</v>
+        <v>-14.39828094465196</v>
       </c>
       <c r="F87">
-        <v>4.721406605220903</v>
+        <v>8.458284617216254</v>
       </c>
       <c r="G87">
-        <v>-10.2160205714894</v>
+        <v>-9.593095606677474</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.640267115036943</v>
       </c>
       <c r="E88">
-        <v>-19.68281872794115</v>
+        <v>-16.0063254586104</v>
       </c>
       <c r="F88">
-        <v>4.453842277381857</v>
+        <v>8.473084229234669</v>
       </c>
       <c r="G88">
-        <v>-9.352255723519569</v>
+        <v>-9.108640618861312</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.332410581163215</v>
       </c>
       <c r="E89">
-        <v>-20.83128548953936</v>
+        <v>-17.8618473757814</v>
       </c>
       <c r="F89">
-        <v>5.511359298082984</v>
+        <v>8.766142392262273</v>
       </c>
       <c r="G89">
-        <v>-9.766801498047197</v>
+        <v>-9.048397687421373</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.970700230431136</v>
       </c>
       <c r="E90">
-        <v>-22.4666622872265</v>
+        <v>-18.76237157449867</v>
       </c>
       <c r="F90">
-        <v>4.596987478055222</v>
+        <v>8.376054241875153</v>
       </c>
       <c r="G90">
-        <v>-9.091550684767883</v>
+        <v>-8.60819743116917</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.561496048896698</v>
       </c>
       <c r="E91">
-        <v>-24.56992325992352</v>
+        <v>-20.23971037485343</v>
       </c>
       <c r="F91">
-        <v>4.95394590253478</v>
+        <v>8.807284087689712</v>
       </c>
       <c r="G91">
-        <v>-9.010612380954189</v>
+        <v>-8.341094762796962</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.118459199208674</v>
       </c>
       <c r="E92">
-        <v>-26.35610316081518</v>
+        <v>-22.46209375476919</v>
       </c>
       <c r="F92">
-        <v>4.609157851937153</v>
+        <v>8.586007273584299</v>
       </c>
       <c r="G92">
-        <v>-7.979222065767339</v>
+        <v>-8.792489891855856</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.651706879265236</v>
       </c>
       <c r="E93">
-        <v>-28.12827843311952</v>
+        <v>-24.84598306347355</v>
       </c>
       <c r="F93">
-        <v>4.832041698803999</v>
+        <v>8.819219205229249</v>
       </c>
       <c r="G93">
-        <v>-8.940913332605238</v>
+        <v>-8.383910974091219</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.175285089119202</v>
       </c>
       <c r="E94">
-        <v>-29.19002198904398</v>
+        <v>-27.55467841704745</v>
       </c>
       <c r="F94">
-        <v>4.778539104991984</v>
+        <v>8.52198441375673</v>
       </c>
       <c r="G94">
-        <v>-9.466445775817979</v>
+        <v>-7.654904929680883</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.700024136409327</v>
       </c>
       <c r="E95">
-        <v>-30.23200456548492</v>
+        <v>-28.96034940278097</v>
       </c>
       <c r="F95">
-        <v>4.818103588884495</v>
+        <v>8.23501972134412</v>
       </c>
       <c r="G95">
-        <v>-7.578410113161263</v>
+        <v>-7.563377445805633</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2332541838708115</v>
       </c>
       <c r="E96">
-        <v>-32.70488058003506</v>
+        <v>-30.63266486199113</v>
       </c>
       <c r="F96">
-        <v>4.447546685120581</v>
+        <v>8.261040398200857</v>
       </c>
       <c r="G96">
-        <v>-7.678148388775564</v>
+        <v>-6.969339064522081</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.21557158385793</v>
       </c>
       <c r="E97">
-        <v>-35.85764767148794</v>
+        <v>-33.56682975196732</v>
       </c>
       <c r="F97">
-        <v>4.206223379867417</v>
+        <v>7.981794433247533</v>
       </c>
       <c r="G97">
-        <v>-8.31010130838356</v>
+        <v>-7.09543280678367</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.6509386693126096</v>
       </c>
       <c r="E98">
-        <v>-38.17964374842404</v>
+        <v>-35.93238263267256</v>
       </c>
       <c r="F98">
-        <v>3.421391654289442</v>
+        <v>8.049848128857123</v>
       </c>
       <c r="G98">
-        <v>-7.008403635838908</v>
+        <v>-6.951476350029683</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.063453032648777</v>
       </c>
       <c r="E99">
-        <v>-38.89746818096211</v>
+        <v>-38.51223706452763</v>
       </c>
       <c r="F99">
-        <v>2.93544979825478</v>
+        <v>7.42337539967233</v>
       </c>
       <c r="G99">
-        <v>-7.441202431175305</v>
+        <v>-6.114769259002151</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.469757789138646</v>
       </c>
       <c r="E100">
-        <v>-42.77400502696455</v>
+        <v>-40.80048622284384</v>
       </c>
       <c r="F100">
-        <v>3.461759654562668</v>
+        <v>7.045003677830405</v>
       </c>
       <c r="G100">
-        <v>-8.310541218847161</v>
+        <v>-6.193887873835838</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.851340659665698</v>
       </c>
       <c r="E101">
-        <v>-44.40068707674315</v>
+        <v>-43.20650384148689</v>
       </c>
       <c r="F101">
-        <v>2.810722518415258</v>
+        <v>6.743105177880126</v>
       </c>
       <c r="G101">
-        <v>-8.118928230326993</v>
+        <v>-6.250527977740042</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.245410730592473</v>
       </c>
       <c r="E102">
-        <v>-48.05827700472894</v>
+        <v>-45.61319843357588</v>
       </c>
       <c r="F102">
-        <v>2.926167113139009</v>
+        <v>6.480486203435793</v>
       </c>
       <c r="G102">
-        <v>-7.1929884999198</v>
+        <v>-5.78741843770082</v>
       </c>
     </row>
   </sheetData>
